--- a/data/processed_car_parts.xlsx
+++ b/data/processed_car_parts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Girpazh\Girpazh_Telbot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973F510A-C0F5-4B33-93DF-EDEB0940B783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5D6041-AEB7-492E-95C8-CE78E42D9687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22222,16 +22222,16 @@
     <t>اورجینال =&gt; 6,825,000</t>
   </si>
   <si>
-    <t>مدل خودرو</t>
-  </si>
-  <si>
-    <t>سال ساخت</t>
-  </si>
-  <si>
-    <t>کد فنی</t>
-  </si>
-  <si>
-    <t>قیمت</t>
+    <t>model</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>price</t>
   </si>
 </sst>
 </file>
